--- a/docentes/Caballero Rosas María Teresa - Estadisticos 20232.xlsx
+++ b/docentes/Caballero Rosas María Teresa - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="26">
   <si>
     <t>Mat</t>
   </si>
@@ -71,6 +71,30 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>ARELI DANAE</t>
+  </si>
+  <si>
+    <t>MARITZA</t>
+  </si>
+  <si>
+    <t>MARYGELLI</t>
   </si>
 </sst>
 </file>
@@ -588,16 +612,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>66.67</v>
+      </c>
+      <c r="H2">
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -611,16 +638,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>69.23</v>
+      </c>
+      <c r="H3">
+        <v>7.2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -634,16 +664,19 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>84.20999999999999</v>
+      </c>
+      <c r="H4">
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -699,16 +732,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>82.05</v>
+        <v>66.67</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -725,16 +758,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>84.62</v>
+        <v>69.23</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -751,16 +784,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>78.95</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -770,7 +803,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -800,6 +833,75 @@
         <v>17</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>23330051920103</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>23330051920139</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>23330051920141</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Caballero Rosas María Teresa - Estadisticos 20232.xlsx
+++ b/docentes/Caballero Rosas María Teresa - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="18">
   <si>
     <t>Mat</t>
   </si>
@@ -71,30 +71,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>ARELI DANAE</t>
-  </si>
-  <si>
-    <t>MARITZA</t>
-  </si>
-  <si>
-    <t>MARYGELLI</t>
   </si>
 </sst>
 </file>
@@ -732,16 +708,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="G2">
-        <v>66.67</v>
+        <v>92.31</v>
       </c>
       <c r="H2">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -758,16 +734,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="G3">
-        <v>69.23</v>
+        <v>92.31</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -784,16 +760,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G4">
-        <v>84.20999999999999</v>
+        <v>97.37</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -803,7 +779,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -833,75 +809,6 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>23330051920103</v>
-      </c>
-      <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>23330051920139</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>23330051920141</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
